--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484713_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484713_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7679</v>
+        <v>7.4747</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2424</v>
+        <v>8.7111</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4745</v>
+        <v>-1.2364</v>
       </c>
       <c r="G2" t="n">
         <v>6.4637</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.194</v>
+        <v>0.5128</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6647999999999999</v>
+        <v>1.1335</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8588</v>
+        <v>-0.6207</v>
       </c>
       <c r="V2" t="n">
         <v>-0.4453</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6832</v>
+        <v>5.9444</v>
       </c>
       <c r="E3" t="n">
-        <v>7.7615</v>
+        <v>6.9433</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0783</v>
+        <v>-0.9989</v>
       </c>
       <c r="G3" t="n">
         <v>1.8432</v>
@@ -688,13 +688,13 @@
         <v>2.2644</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4625</v>
+        <v>1.7237</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0815</v>
+        <v>1.2634</v>
       </c>
       <c r="U3" t="n">
-        <v>0.381</v>
+        <v>0.4603</v>
       </c>
       <c r="V3" t="n">
         <v>0.3018</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.4275</v>
+        <v>5.0823</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8256</v>
+        <v>3.5333</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6019</v>
+        <v>1.549</v>
       </c>
       <c r="G4" t="n">
         <v>2.3139</v>
@@ -766,13 +766,13 @@
         <v>0.7548</v>
       </c>
       <c r="S4" t="n">
-        <v>0.472</v>
+        <v>0.1268</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1793</v>
+        <v>-0.113</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2928</v>
+        <v>0.2399</v>
       </c>
       <c r="V4" t="n">
         <v>1.8868</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0903</v>
+        <v>3.9097</v>
       </c>
       <c r="E5" t="n">
-        <v>3.176</v>
+        <v>2.9425</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9143</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>2.9569</v>
@@ -844,13 +844,13 @@
         <v>0.9435</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1334</v>
+        <v>0.9528</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0052</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1282</v>
+        <v>0.1811</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. CAMARA</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9444</v>
+        <v>3.0686</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9373</v>
+        <v>4.0391</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0071</v>
+        <v>-0.9705</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1729</v>
+        <v>2.0677</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6425</v>
+        <v>-0.1964</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5303</v>
+        <v>2.2641</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4264</v>
+        <v>5.0939</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1385</v>
+        <v>0.4703</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2879</v>
+        <v>4.6236</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5993</v>
+        <v>-3.0262</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.781</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8182</v>
+        <v>-2.3595</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7548</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1322</v>
+        <v>-2.0757</v>
       </c>
       <c r="R6" t="n">
-        <v>1.887</v>
+        <v>1.3209</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7399</v>
+        <v>1.4539</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7187</v>
+        <v>0.7191</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0212</v>
+        <v>0.7348</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6226</v>
+        <v>0.3018</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9244</v>
+        <v>0.3018</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2614</v>
+        <v>2.1416</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9673</v>
+        <v>4.2558</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7059</v>
+        <v>-2.1142</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0677</v>
+        <v>0.1449</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1964</v>
+        <v>0.6018</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2641</v>
+        <v>-0.457</v>
       </c>
       <c r="J7" t="n">
-        <v>5.0939</v>
+        <v>2.4029</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4703</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>4.6236</v>
+        <v>1.6211</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0262</v>
+        <v>-2.258</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.18</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.3595</v>
+        <v>-2.0781</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7548</v>
+        <v>1.5096</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0757</v>
+        <v>-0.1887</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6467000000000001</v>
+        <v>1.1097</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3527</v>
+        <v>0.7963</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9994</v>
+        <v>0.3134</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3018</v>
+        <v>-0.6226</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4279</v>
+        <v>1.5559</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3423</v>
+        <v>2.2852</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9144</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0.3185</v>
@@ -1078,13 +1078,13 @@
         <v>1.6983</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.7958</v>
       </c>
       <c r="T8" t="n">
-        <v>1.138</v>
+        <v>1.0808</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4702</v>
+        <v>-0.285</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1245</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. BOUNDI</t>
+          <t>O. CAMARA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0728</v>
+        <v>1.2075</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.01</v>
+        <v>1.7295</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0828</v>
+        <v>-0.522</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3377</v>
+        <v>-2.1729</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1988</v>
+        <v>-0.6425</v>
       </c>
       <c r="I9" t="n">
-        <v>0.139</v>
+        <v>-1.5303</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4956</v>
+        <v>0.4264</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2488</v>
+        <v>0.1385</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2468</v>
+        <v>0.2879</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1579</v>
+        <v>-2.5993</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0501</v>
+        <v>-0.781</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1078</v>
+        <v>-1.8182</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5096</v>
+        <v>0.7548</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.8305</v>
+        <v>-1.1322</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3209</v>
+        <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>1.124</v>
+        <v>2.0029</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4761</v>
+        <v>1.5109</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6479</v>
+        <v>0.4921</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1207</v>
+        <v>0.6226</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8488</v>
+        <v>0.9244</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7281</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. MOLLERMARK</t>
+          <t>T. BOUNDI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5347</v>
+        <v>0.8607</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2474</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7821</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3276</v>
+        <v>0.3377</v>
       </c>
       <c r="H10" t="n">
-        <v>1.033</v>
+        <v>0.1988</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2946</v>
+        <v>0.139</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9923</v>
+        <v>0.4956</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6762</v>
+        <v>0.2488</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3162</v>
+        <v>0.2468</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3353</v>
+        <v>-0.1579</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3569</v>
+        <v>-0.0501</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0216</v>
+        <v>-0.1078</v>
       </c>
       <c r="P10" t="n">
         <v>-1.5096</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2833</v>
+        <v>0.9119</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3527</v>
+        <v>0.555</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0694</v>
+        <v>0.3569</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.1207</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8488</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.7281</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>R. MOLLERMARK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.531</v>
+        <v>0.7438</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9891</v>
+        <v>-0.0912</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4581</v>
+        <v>0.835</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1449</v>
+        <v>2.3276</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6018</v>
+        <v>1.033</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.457</v>
+        <v>1.2946</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4029</v>
+        <v>1.9923</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.6762</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6211</v>
+        <v>1.3162</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.258</v>
+        <v>0.3353</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.18</v>
+        <v>0.3569</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.0781</v>
+        <v>-0.0216</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5096</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6983</v>
+        <v>0.3774</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5009</v>
+        <v>-0.0742</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4703</v>
+        <v>-0.1965</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0306</v>
+        <v>0.1223</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. MEJIA ACOSTA</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.247</v>
+        <v>-0.3393</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6328</v>
+        <v>-1.0374</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6142</v>
+        <v>0.698</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5175</v>
+        <v>-0.4622</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4743</v>
+        <v>0.0313</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0433</v>
+        <v>-0.4936</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9258</v>
+        <v>-0.5901</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2911</v>
+        <v>0.6182</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2169</v>
+        <v>-1.2083</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5918</v>
+        <v>0.1279</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7654</v>
+        <v>-0.5869</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1736</v>
+        <v>0.7148</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3774</v>
+        <v>0.3774</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1499</v>
+        <v>0.1718</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2556</v>
+        <v>0.4962</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1057</v>
+        <v>-0.3244</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4981</v>
+        <v>-0.4263</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>-0.4263</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>G. MEJIA ACOSTA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3758</v>
+        <v>-1.3559</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2855</v>
+        <v>-1.1385</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9097</v>
+        <v>-0.2174</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4622</v>
+        <v>-1.5175</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0313</v>
+        <v>-0.4743</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4936</v>
+        <v>-1.0433</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5901</v>
+        <v>-0.9258</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6182</v>
+        <v>0.2911</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2083</v>
+        <v>-1.2169</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1279</v>
+        <v>-0.5918</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5869</v>
+        <v>-0.7654</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7148</v>
+        <v>0.1736</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3774</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8647</v>
+        <v>0.041</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7519</v>
+        <v>0.7499</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1128</v>
+        <v>-0.7089</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4263</v>
+        <v>0.4981</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X13" t="n">
         <v>-0.4263</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>29.1183</v>
+        <v>30.294</v>
       </c>
       <c r="E14" t="n">
-        <v>31.0658</v>
+        <v>32.2417</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9475</v>
+        <v>-1.947700000000001</v>
       </c>
       <c r="G14" t="n">
         <v>14.6215</v>
       </c>
       <c r="H14" t="n">
-        <v>7.152899999999999</v>
+        <v>7.1529</v>
       </c>
       <c r="I14" t="n">
-        <v>7.468699999999997</v>
+        <v>7.468699999999998</v>
       </c>
       <c r="J14" t="n">
         <v>29.628</v>
@@ -1534,7 +1534,7 @@
         <v>-6.6755</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.331099999999999</v>
+        <v>-8.331099999999998</v>
       </c>
       <c r="P14" t="n">
         <v>2.8305</v>
@@ -1546,19 +1546,19 @@
         <v>16.983</v>
       </c>
       <c r="S14" t="n">
-        <v>8.5533</v>
+        <v>9.728899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>7.591600000000001</v>
+        <v>8.767299999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9618</v>
+        <v>0.9618000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>3.1131</v>
       </c>
       <c r="W14" t="n">
-        <v>7.998800000000001</v>
+        <v>7.9988</v>
       </c>
       <c r="X14" t="n">
         <v>-4.885700000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CONNELLY IV</t>
+          <t>T. SODERMAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6539</v>
+        <v>2.6141</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9677</v>
+        <v>6.5266</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3137</v>
+        <v>-3.9125</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6116</v>
+        <v>3.372</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6808</v>
+        <v>0.8069</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0692</v>
+        <v>2.5651</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6194</v>
+        <v>6.5522</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4293</v>
+        <v>3.3597</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1901</v>
+        <v>3.1926</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.0077</v>
+        <v>-3.1803</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.7484</v>
+        <v>-2.5528</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2593</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.6983</v>
+        <v>0.5661</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0757</v>
+        <v>1.5096</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5296999999999999</v>
+        <v>-0.8183</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7265</v>
+        <v>-0.0065</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1968</v>
+        <v>-0.8118</v>
       </c>
       <c r="V15" t="n">
-        <v>3.211</v>
+        <v>-0.5057</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3958</v>
+        <v>0.9244</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1849</v>
+        <v>-1.4301</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. SODERMAN</t>
+          <t>J. CONNELLY IV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9598</v>
+        <v>1.9263</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1369</v>
+        <v>3.4805</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.1771</v>
+        <v>-1.5542</v>
       </c>
       <c r="G16" t="n">
-        <v>3.372</v>
+        <v>0.6116</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8069</v>
+        <v>0.6808</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5651</v>
+        <v>-0.0692</v>
       </c>
       <c r="J16" t="n">
-        <v>6.5522</v>
+        <v>3.6194</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3597</v>
+        <v>3.4293</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1926</v>
+        <v>0.1901</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.1803</v>
+        <v>-3.0077</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.5528</v>
+        <v>-2.7484</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.2593</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5661</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5096</v>
+        <v>2.0757</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4726</v>
+        <v>-0.198</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3963</v>
+        <v>0.2393</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0763</v>
+        <v>-0.4373</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5057</v>
+        <v>3.211</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9244</v>
+        <v>3.3958</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4301</v>
+        <v>-0.1849</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.6989</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3014</v>
+        <v>-1.204</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5051</v>
       </c>
       <c r="G17" t="n">
         <v>-1.3454</v>
@@ -1780,13 +1780,13 @@
         <v>0.9435</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3415</v>
+        <v>-0.297</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3404</v>
+        <v>-0.243</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0012</v>
+        <v>-0.0541</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>A. FERRIZ SELLES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7608</v>
+        <v>-1.4001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5249</v>
+        <v>3.2504</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2857</v>
+        <v>-4.6505</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6367</v>
+        <v>-0.5994</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5862000000000001</v>
+        <v>-0.8507</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2229</v>
+        <v>0.2513</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2057</v>
+        <v>3.3868</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7662</v>
+        <v>0.5815</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4396</v>
+        <v>2.8054</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8424</v>
+        <v>-3.9862</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.18</v>
+        <v>-1.4321</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.6624</v>
+        <v>-2.5541</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3774</v>
+        <v>1.5096</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5961</v>
+        <v>-0.5784</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2627</v>
+        <v>-0.1365</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8588</v>
+        <v>-0.442</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9054</v>
+        <v>-1.7319</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9054</v>
+        <v>-1.7319</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FERRIZ SELLES</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9197</v>
+        <v>-1.9496</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8606</v>
+        <v>1.2326</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.7804</v>
+        <v>-3.1823</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5994</v>
+        <v>-0.6367</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8507</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2513</v>
+        <v>-1.2229</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3868</v>
+        <v>2.2057</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5815</v>
+        <v>0.7662</v>
       </c>
       <c r="L19" t="n">
-        <v>2.8054</v>
+        <v>1.4396</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.9862</v>
+        <v>-2.8424</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4321</v>
+        <v>-0.18</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.5541</v>
+        <v>-2.6624</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0981</v>
+        <v>-0.7849</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5262</v>
+        <v>-0.0296</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5719</v>
+        <v>-0.7553</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.7319</v>
+        <v>-0.9054</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7319</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.053</v>
+        <v>-2.0711</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4135</v>
+        <v>1.3161</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4665</v>
+        <v>-3.3872</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8578</v>
@@ -2014,13 +2014,13 @@
         <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8783</v>
+        <v>-0.8963</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1735</v>
+        <v>-0.2709</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7048</v>
+        <v>-0.6254</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5057</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5382</v>
+        <v>-2.9628</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3406</v>
+        <v>-2.6329</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1976</v>
+        <v>-0.3299</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4457</v>
@@ -2092,13 +2092,13 @@
         <v>0.9435</v>
       </c>
       <c r="S21" t="n">
-        <v>0.549</v>
+        <v>0.1245</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4391</v>
+        <v>0.1468</v>
       </c>
       <c r="U21" t="n">
-        <v>0.11</v>
+        <v>-0.0223</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6415999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0982</v>
+        <v>-3.7182</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5018</v>
+        <v>0.6967</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.6</v>
+        <v>-4.4148</v>
       </c>
       <c r="G22" t="n">
         <v>-0.104</v>
@@ -2170,13 +2170,13 @@
         <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5037</v>
+        <v>-1.1237</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3281</v>
+        <v>-0.1332</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1757</v>
+        <v>-0.9905</v>
       </c>
       <c r="V22" t="n">
         <v>-1.547</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0174</v>
+        <v>-5.6494</v>
       </c>
       <c r="E23" t="n">
         <v>-2.7012</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3162</v>
+        <v>-2.9482</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7353</v>
@@ -2248,13 +2248,13 @@
         <v>0.7548</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9611</v>
+        <v>-0.5931</v>
       </c>
       <c r="T23" t="n">
         <v>0.0617</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0228</v>
+        <v>-0.6548</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3018</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4236</v>
+        <v>-6.0808</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4933</v>
+        <v>-2.201</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9303</v>
+        <v>-3.8798</v>
       </c>
       <c r="G24" t="n">
         <v>-4.193</v>
@@ -2326,13 +2326,13 @@
         <v>1.6983</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.178</v>
+        <v>-1.8351</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6438</v>
+        <v>-0.3515</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5342</v>
+        <v>-1.4836</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8075</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.1775</v>
+        <v>-8.4781</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.6211</v>
+        <v>-5.816</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5564</v>
+        <v>-2.6622</v>
       </c>
       <c r="G25" t="n">
         <v>-6.6879</v>
@@ -2404,13 +2404,13 @@
         <v>1.3209</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6025</v>
+        <v>-0.9032</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0436</v>
+        <v>-0.2384</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>0.6226</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-29.11810000000001</v>
+        <v>-28.4686</v>
       </c>
       <c r="E26" t="n">
-        <v>1.947799999999999</v>
+        <v>1.947800000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-31.0659</v>
+        <v>-30.4165</v>
       </c>
       <c r="G26" t="n">
         <v>-14.6216</v>
@@ -2458,7 +2458,7 @@
         <v>15.0065</v>
       </c>
       <c r="K26" t="n">
-        <v>6.675500000000001</v>
+        <v>6.6755</v>
       </c>
       <c r="L26" t="n">
         <v>8.331299999999999</v>
@@ -2482,13 +2482,13 @@
         <v>14.1525</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.5532</v>
+        <v>-7.903499999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9619</v>
+        <v>-0.9618</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.591500000000001</v>
+        <v>-6.9419</v>
       </c>
       <c r="V26" t="n">
         <v>-3.113</v>
